--- a/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:18</t>
+    <t xml:space="preserve">2026-09-10 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:32</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
@@ -48,15 +48,15 @@
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puqueldón</t>
   </si>
   <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fresia</t>
   </si>
   <si>
@@ -72,15 +72,15 @@
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
@@ -105,12 +105,12 @@
     <t xml:space="preserve">Hualaihué</t>
   </si>
   <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Futaleufú</t>
   </si>
   <si>
-    <t xml:space="preserve">Castro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,7 +568,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>165.44</v>
+        <v>178.89</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>161.3</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="4">
@@ -602,7 +602,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>157.12</v>
+        <v>168.7</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +619,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>150.85</v>
+        <v>161.93</v>
       </c>
     </row>
     <row r="6">
@@ -630,13 +630,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10206</v>
+        <v>10210</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>142.94</v>
+        <v>155.72</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>141.39</v>
+        <v>154.88</v>
       </c>
     </row>
     <row r="8">
@@ -664,13 +664,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10210</v>
+        <v>10206</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>141.26</v>
+        <v>154.87</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>138.48</v>
+        <v>149.47</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>137.32</v>
+        <v>147.9</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>134.42</v>
+        <v>145.21</v>
       </c>
     </row>
     <row r="12">
@@ -738,7 +738,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>133.01</v>
+        <v>143.08</v>
       </c>
     </row>
     <row r="13">
@@ -755,7 +755,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>131.74</v>
+        <v>140.99</v>
       </c>
     </row>
     <row r="14">
@@ -766,13 +766,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>10106</v>
+        <v>10204</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>125.26</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="15">
@@ -783,13 +783,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10202</v>
+        <v>10106</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>125.18</v>
+        <v>135.64</v>
       </c>
     </row>
     <row r="16">
@@ -800,13 +800,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10204</v>
+        <v>10202</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>122.66</v>
+        <v>135.17</v>
       </c>
     </row>
     <row r="17">
@@ -823,7 +823,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>122.13</v>
+        <v>131.46</v>
       </c>
     </row>
     <row r="18">
@@ -840,7 +840,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>120.84</v>
+        <v>129.77</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>115.51</v>
+        <v>125.18</v>
       </c>
     </row>
     <row r="20">
@@ -874,7 +874,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>108.91</v>
+        <v>117.41</v>
       </c>
     </row>
     <row r="21">
@@ -891,7 +891,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>108.25</v>
+        <v>116.93</v>
       </c>
     </row>
     <row r="22">
@@ -908,7 +908,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>106.71</v>
+        <v>115.39</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>103.7</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="24">
@@ -942,7 +942,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>98.39</v>
+        <v>106.38</v>
       </c>
     </row>
     <row r="25">
@@ -953,13 +953,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10402</v>
+        <v>10201</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>93.37</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="26">
@@ -970,13 +970,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10201</v>
+        <v>10402</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>92.4</v>
+        <v>100.16</v>
       </c>
     </row>
     <row r="27">
@@ -993,7 +993,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>89.83</v>
+        <v>96.06</v>
       </c>
     </row>
     <row r="28">
@@ -1010,7 +1010,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>88.02</v>
+        <v>95.44</v>
       </c>
     </row>
     <row r="29">
@@ -1027,7 +1027,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>82.54</v>
+        <v>87.98</v>
       </c>
     </row>
     <row r="30">
@@ -1044,7 +1044,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>74.35</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="31">
@@ -1061,7 +1061,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>64.96</v>
+        <v>69.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:12</t>
+    <t xml:space="preserve">2026-10-02 16:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:05</t>
+    <t xml:space="preserve">2026-10-05 16:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
